--- a/miranda_sales_analysis.results.Q4.xlsx
+++ b/miranda_sales_analysis.results.Q4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B2B28D61-42CE-4BD8-B6CC-82A27574BBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE7E917-B80A-4811-B42E-1FAFB3A24503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{17CDDE66-8F87-45C7-A9F7-9B7BDC9E9294}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -554,7 +554,6 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -562,6 +561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -918,20 +918,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -988,20 +975,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4926,7 +4900,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{085E9ECE-2A34-444C-A493-20F9205165EC}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{085E9ECE-2A34-444C-A493-20F9205165EC}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:C46" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0">
@@ -5728,8 +5702,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="12" width="24.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="26.90625" bestFit="1" customWidth="1"/>
@@ -5737,7 +5711,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
@@ -5748,475 +5722,475 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1300</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>3046.54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>266</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4">
         <v>123.03999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>205</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="4">
         <v>127.47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>119</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="4">
         <v>111.24</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>287</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="4">
         <v>36.29</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>274</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="4">
         <v>1957.4499999999998</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>149</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="4">
         <v>691.05</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>4</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>1534</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="4">
         <v>2975.24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>337</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="4">
         <v>128.43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>276</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="4">
         <v>129.88</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>120</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="4">
         <v>111.77</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>370</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="4">
         <v>39.520000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>253</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="4">
         <v>1853.8899999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>178</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="4">
         <v>711.75</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>6</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>1527</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="4">
         <v>2868.46</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>314</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="4">
         <v>120.08999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>252</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="4">
         <v>126.75000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>137</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="4">
         <v>118.33000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>339</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="4">
         <v>40.269999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>271</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="4">
         <v>1737.14</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>214</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="4">
         <v>725.87999999999988</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>8</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>1423</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="4">
         <v>3008.1900000000005</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>250</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="4">
         <v>126.75</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>221</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="4">
         <v>133.59</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>95</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="4">
         <v>111.52</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>291</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="4">
         <v>40.98</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>327</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="4">
         <v>1904.67</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>239</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="4">
         <v>690.68000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>10</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>1736</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="4">
         <v>3004.1899999999996</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>331</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="4">
         <v>136.44</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>284</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="4">
         <v>121.73</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>111</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="4">
         <v>116.16</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>362</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="4">
         <v>40.42</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>386</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="4">
         <v>1911.54</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>262</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="4">
         <v>677.89999999999986</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>12</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>1398</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="4">
         <v>2967.5899999999997</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="4">
         <v>272</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="4">
         <v>128.72</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="4">
         <v>210</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="4">
         <v>125.13000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="4">
         <v>114</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="4">
         <v>123.82</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="4">
         <v>280</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="4">
         <v>40.17</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="4">
         <v>334</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="4">
         <v>1892.05</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="4">
         <v>188</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="4">
         <v>657.69999999999993</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="4">
         <v>8918</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="4">
         <v>17870.21</v>
       </c>
     </row>
